--- a/localRun/tseadfwd/input/PARAMETRAGE_corrected.xlsx
+++ b/localRun/tseadfwd/input/PARAMETRAGE_corrected.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mehdi\IdeaProjects\file_transform_engine\localRun\tseadfwd\input\"/>
     </mc:Choice>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="84">
   <si>
     <t>PERIMETER</t>
   </si>
@@ -269,12 +269,19 @@
   </si>
   <si>
     <t>69549</t>
+  </si>
+  <si>
+    <t>OLA</t>
+  </si>
+  <si>
+    <t>LS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
       <sz val="11"/>
@@ -654,17 +661,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="11.53125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.86328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.06640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.06640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.19921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.1328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="12.0"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="11.53125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="11.86328125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="15.06640625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="29.06640625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="20.19921875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="18.1328125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="21.73046875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -2053,6 +2060,206 @@
       </c>
       <c r="H67" s="2"/>
     </row>
+    <row r="68">
+      <c r="A68" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H67" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
